--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eirar\Polla\Pauta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FAAB85-18A5-4C7F-9714-3AAE92E530BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09380DF-5755-45A7-9294-7EF3224D1970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="63">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,6 +213,18 @@
   </si>
   <si>
     <t>Colombia</t>
+  </si>
+  <si>
+    <t>Gana México</t>
+  </si>
+  <si>
+    <t>Gana Paraguay</t>
+  </si>
+  <si>
+    <t>Gana Brasil</t>
+  </si>
+  <si>
+    <t>Gana Australia</t>
   </si>
 </sst>
 </file>
@@ -391,27 +403,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -431,6 +422,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -773,41 +785,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F1176-9B5F-4509-AEB9-C4D2AF7AA58E}">
   <dimension ref="B2:H104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.53125" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="3.53125" customWidth="1"/>
-    <col min="4" max="4" width="14.73046875" customWidth="1"/>
-    <col min="8" max="8" width="21.796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" customWidth="1"/>
+    <col min="3" max="3" width="3.54296875" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="8" max="8" width="21.81640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="3" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="15" t="s">
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-    </row>
-    <row r="4" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
-    </row>
-    <row r="5" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="6" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="6" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4" t="s">
         <v>37</v>
       </c>
@@ -822,27 +836,29 @@
         <v>Gana Sudáfrica</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+    <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="10" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="6" t="s">
+    <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4" t="s">
         <v>40</v>
       </c>
@@ -857,27 +873,29 @@
         <v>Gana Paraguay</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+    <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="14" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="6" t="s">
+    <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
@@ -892,27 +910,29 @@
         <v>Gana Marruecos</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+    <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="18" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="6" t="s">
+    <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
@@ -928,27 +948,29 @@
         <v>Gana Turquía</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+    <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="22" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="6" t="s">
+    <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="4" t="s">
         <v>45</v>
       </c>
@@ -963,27 +985,27 @@
         <v>Gana Japón</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+    <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="26" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="6" t="s">
+    <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="4" t="s">
         <v>46</v>
       </c>
@@ -998,27 +1020,27 @@
         <v>Gana Egipto</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+    <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="30" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B30" s="6" t="s">
+    <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="4" t="s">
         <v>5</v>
       </c>
@@ -1033,27 +1055,27 @@
         <v>Gana Senegal</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+    <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="34" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="6" t="s">
+    <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="4" t="s">
         <v>10</v>
       </c>
@@ -1068,27 +1090,27 @@
         <v>Gana Argelia</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+    <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B38" s="6" t="s">
+    <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="4" t="s">
         <v>49</v>
       </c>
@@ -1104,27 +1126,27 @@
         <v>Gana Croacia</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+    <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="42" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B42" s="6" t="s">
+    <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="43" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="4" t="s">
         <v>37</v>
       </c>
@@ -1139,27 +1161,27 @@
         <v>Gana Corea</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+    <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="46" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B46" s="6" t="s">
+    <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="4" t="s">
         <v>40</v>
       </c>
@@ -1174,27 +1196,27 @@
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+    <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="50" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B50" s="6" t="s">
+    <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
       </c>
     </row>
-    <row r="51" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="51" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="4" t="s">
         <v>45</v>
       </c>
@@ -1209,27 +1231,27 @@
         <v>Gana Suecia</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+    <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="54" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B54" s="6" t="s">
+    <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
       </c>
     </row>
-    <row r="55" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="4" t="s">
         <v>46</v>
       </c>
@@ -1244,27 +1266,27 @@
         <v>Gana Irán</v>
       </c>
     </row>
-    <row r="56" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+    <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="58" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B58" s="6" t="s">
+    <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
       </c>
     </row>
-    <row r="59" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="4" t="s">
         <v>10</v>
       </c>
@@ -1280,27 +1302,27 @@
         <v>Gana Austria</v>
       </c>
     </row>
-    <row r="60" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+    <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="62" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B62" s="6" t="s">
+    <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="4" t="s">
         <v>53</v>
       </c>
@@ -1315,27 +1337,27 @@
         <v>Gana Senegal</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+    <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="66" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B66" s="6" t="s">
+    <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="67" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="4" t="s">
         <v>54</v>
       </c>
@@ -1350,27 +1372,27 @@
         <v>Gana Canadá</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+    <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="70" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B70" s="6" t="s">
+    <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="4" t="s">
         <v>56</v>
       </c>
@@ -1385,27 +1407,27 @@
         <v>Gana Alemania</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+    <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="74" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B74" s="6" t="s">
+    <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="75" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B75" s="4" t="s">
         <v>27</v>
       </c>
@@ -1420,27 +1442,27 @@
         <v>Gana Suecia</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+    <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="78" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B78" s="6" t="s">
+    <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="79" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B79" s="4" t="s">
         <v>44</v>
       </c>
@@ -1456,27 +1478,27 @@
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+    <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="82" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B82" s="6" t="s">
+    <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B83" s="4" t="s">
         <v>41</v>
       </c>
@@ -1491,27 +1513,27 @@
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+    <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="86" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B86" s="6" t="s">
+    <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="87" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B87" s="4" t="s">
         <v>57</v>
       </c>
@@ -1526,27 +1548,27 @@
         <v>Gana España</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+    <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="90" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B90" s="6" t="s">
+    <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="91" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B91" s="4" t="s">
         <v>53</v>
       </c>
@@ -1561,27 +1583,27 @@
         <v>Gana Francia</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+    <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="94" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B94" s="6" t="s">
+    <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="4" t="s">
         <v>47</v>
       </c>
@@ -1596,27 +1618,27 @@
         <v>Gana Irán</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+    <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="98" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B98" s="6" t="s">
+    <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="4" t="s">
         <v>48</v>
       </c>
@@ -1631,27 +1653,27 @@
         <v>Gana Austria</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+    <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="102" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B102" s="6" t="s">
+    <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="103" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B103" s="4" t="s">
         <v>58</v>
       </c>
@@ -1666,10 +1688,10 @@
         <v>Gana Portugal</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+    <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1677,6 +1699,42 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1693,42 +1751,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09380DF-5755-45A7-9294-7EF3224D1970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AC6687-1352-47A2-8C40-82E6117475E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,18 +213,6 @@
   </si>
   <si>
     <t>Colombia</t>
-  </si>
-  <si>
-    <t>Gana México</t>
-  </si>
-  <si>
-    <t>Gana Paraguay</t>
-  </si>
-  <si>
-    <t>Gana Brasil</t>
-  </si>
-  <si>
-    <t>Gana Australia</t>
   </si>
 </sst>
 </file>
@@ -403,6 +391,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -422,27 +431,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -796,26 +784,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -837,22 +823,20 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -874,22 +858,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -911,22 +893,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -949,22 +929,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -986,20 +964,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1021,20 +999,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1056,20 +1034,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1091,20 +1069,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1127,20 +1105,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1162,20 +1140,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1197,20 +1175,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1232,20 +1210,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1267,20 +1245,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1303,20 +1281,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1338,20 +1316,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1373,20 +1351,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1408,20 +1386,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1443,20 +1421,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1479,20 +1457,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1514,20 +1492,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1549,20 +1527,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1584,20 +1562,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1619,20 +1597,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1654,20 +1632,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1689,9 +1667,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1699,42 +1677,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1751,6 +1693,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AC6687-1352-47A2-8C40-82E6117475E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008083D1-DC35-48E6-BE91-577947FAB37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -391,27 +391,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -431,6 +410,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,24 +784,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -823,20 +823,20 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -858,20 +858,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -893,20 +893,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -929,20 +929,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -964,20 +964,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -999,20 +999,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1034,20 +1034,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1069,20 +1069,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1105,20 +1105,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1140,20 +1140,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1175,20 +1175,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1210,20 +1210,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1245,20 +1245,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1281,20 +1281,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1316,20 +1316,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1351,20 +1351,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1386,20 +1386,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1421,20 +1421,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1457,20 +1457,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1492,20 +1492,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1527,20 +1527,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1562,20 +1562,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1597,20 +1597,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1632,20 +1632,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1667,16 +1667,52 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1693,42 +1729,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008083D1-DC35-48E6-BE91-577947FAB37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4043119-5AAF-499B-A3EA-A3600C30ED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,6 +213,15 @@
   </si>
   <si>
     <t>Colombia</t>
+  </si>
+  <si>
+    <t>Gana México</t>
+  </si>
+  <si>
+    <t>Gana Paraguay</t>
+  </si>
+  <si>
+    <t>Gana Brasil</t>
   </si>
 </sst>
 </file>
@@ -391,6 +400,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -410,27 +440,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,24 +793,26 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -823,20 +834,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -858,20 +871,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -893,20 +908,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -929,20 +946,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -964,20 +981,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -999,20 +1016,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1034,20 +1051,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1069,20 +1086,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1105,20 +1122,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1140,20 +1157,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1175,20 +1192,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1210,20 +1227,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1245,20 +1262,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1281,20 +1298,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1316,20 +1333,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1351,20 +1368,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1386,20 +1403,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1421,20 +1438,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1457,20 +1474,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1492,20 +1509,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1527,20 +1544,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1562,20 +1579,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1597,20 +1614,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1632,20 +1649,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1667,9 +1684,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1677,42 +1694,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1729,6 +1710,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4043119-5AAF-499B-A3EA-A3600C30ED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB0A30A-2839-4022-917F-0F03F7EBC106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,15 +213,6 @@
   </si>
   <si>
     <t>Colombia</t>
-  </si>
-  <si>
-    <t>Gana México</t>
-  </si>
-  <si>
-    <t>Gana Paraguay</t>
-  </si>
-  <si>
-    <t>Gana Brasil</t>
   </si>
 </sst>
 </file>
@@ -400,27 +391,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -440,6 +410,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -793,26 +784,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -834,22 +823,20 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -871,22 +858,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -908,22 +893,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -946,20 +929,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -981,20 +964,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1016,20 +999,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1051,20 +1034,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1086,20 +1069,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1122,20 +1105,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1157,20 +1140,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1192,20 +1175,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1227,20 +1210,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1262,20 +1245,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1298,20 +1281,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1333,20 +1316,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1368,20 +1351,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1403,20 +1386,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1438,20 +1421,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1474,20 +1457,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1509,20 +1492,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1544,20 +1527,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1579,20 +1562,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1614,20 +1597,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1649,20 +1632,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1684,9 +1667,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1694,6 +1677,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1710,42 +1729,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB0A30A-2839-4022-917F-0F03F7EBC106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09941CAB-0568-4713-84D3-C2C25FA276D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -391,6 +391,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -410,27 +431,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,24 +784,26 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -823,20 +825,20 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -858,20 +860,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -893,20 +895,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -929,20 +931,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -964,20 +966,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -999,20 +1001,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1034,20 +1036,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1069,20 +1071,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1105,20 +1107,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1140,20 +1142,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1175,20 +1177,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1210,20 +1212,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1245,20 +1247,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1281,20 +1283,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1316,20 +1318,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1351,20 +1353,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1386,20 +1388,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1421,20 +1423,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1457,20 +1459,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1492,20 +1494,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1527,20 +1529,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1562,20 +1564,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1597,20 +1599,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1632,20 +1634,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1667,9 +1669,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1677,42 +1679,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1729,6 +1695,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09941CAB-0568-4713-84D3-C2C25FA276D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D0C29C-EBBF-482C-ACCC-1519C0627458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -391,27 +391,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -431,6 +410,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,26 +784,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -825,20 +823,20 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -860,20 +858,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -895,20 +893,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -931,20 +929,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -966,20 +964,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1001,20 +999,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1036,20 +1034,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1071,20 +1069,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1107,20 +1105,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1142,20 +1140,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1177,20 +1175,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1212,20 +1210,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1247,20 +1245,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1283,20 +1281,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1318,20 +1316,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1353,20 +1351,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1388,20 +1386,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1423,20 +1421,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1459,20 +1457,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1494,20 +1492,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1529,20 +1527,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1564,20 +1562,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1599,20 +1597,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1634,20 +1632,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1669,9 +1667,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1679,6 +1677,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1695,42 +1729,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D0C29C-EBBF-482C-ACCC-1519C0627458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B3EC71-E56C-44FF-BC5D-B5A310D0F0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="76">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,6 +213,57 @@
   </si>
   <si>
     <t>Colombia</t>
+  </si>
+  <si>
+    <t>Gana Paraguay</t>
+  </si>
+  <si>
+    <t>Gana Brasil</t>
+  </si>
+  <si>
+    <t>Gana Australia</t>
+  </si>
+  <si>
+    <t>Gana Bélgica</t>
+  </si>
+  <si>
+    <t>Gana Argentina</t>
+  </si>
+  <si>
+    <t>Gana Croacia</t>
+  </si>
+  <si>
+    <t>Gana Corea</t>
+  </si>
+  <si>
+    <t>Gana Estados Unidos</t>
+  </si>
+  <si>
+    <t>Gana Suiza</t>
+  </si>
+  <si>
+    <t>Gana Noruega</t>
+  </si>
+  <si>
+    <t>Gana Ecuador</t>
+  </si>
+  <si>
+    <t>Gana Japón</t>
+  </si>
+  <si>
+    <t>Gana España</t>
+  </si>
+  <si>
+    <t>Gana Francia</t>
+  </si>
+  <si>
+    <t>Gana Irán</t>
+  </si>
+  <si>
+    <t>Gana Austria</t>
+  </si>
+  <si>
+    <t>Gana Portugal</t>
   </si>
 </sst>
 </file>
@@ -391,6 +442,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -410,27 +482,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,24 +835,26 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -823,20 +876,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -858,20 +913,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -893,20 +950,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -929,20 +988,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -964,20 +1025,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -999,20 +1060,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1034,20 +1097,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1069,20 +1134,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1105,20 +1172,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1140,20 +1209,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1175,20 +1246,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1210,20 +1283,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1245,20 +1320,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1281,20 +1356,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1316,20 +1393,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1351,20 +1430,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1386,20 +1467,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1421,20 +1504,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1457,20 +1542,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1492,20 +1579,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1527,20 +1616,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1562,20 +1653,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1597,20 +1690,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1632,20 +1727,22 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1667,9 +1764,11 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1677,42 +1776,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1729,6 +1792,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B3EC71-E56C-44FF-BC5D-B5A310D0F0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6712AC-CD18-498F-8E56-CB8EFE944BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="76">
   <si>
     <t>Partido 1</t>
   </si>
@@ -442,27 +442,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -482,6 +461,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -835,26 +835,26 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -876,22 +876,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -913,22 +913,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -950,22 +950,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -988,22 +988,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1025,20 +1025,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1060,22 +1062,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1097,22 +1099,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1134,22 +1136,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1172,22 +1174,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1209,22 +1211,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1246,22 +1248,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1283,22 +1285,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1320,20 +1322,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1356,22 +1360,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1393,22 +1397,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1430,22 +1434,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1467,22 +1471,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1504,22 +1508,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1542,22 +1546,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1579,22 +1583,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1616,22 +1620,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1653,22 +1657,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1690,22 +1694,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1727,22 +1731,22 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9" t="s">
+      <c r="B100" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1764,11 +1768,11 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9" t="s">
+      <c r="B104" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1776,6 +1780,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1792,42 +1832,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6712AC-CD18-498F-8E56-CB8EFE944BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B053078-BA77-4CA5-A64A-6DBF88E011FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="77">
   <si>
     <t>Partido 1</t>
   </si>
@@ -221,9 +221,6 @@
     <t>Gana Brasil</t>
   </si>
   <si>
-    <t>Gana Australia</t>
-  </si>
-  <si>
     <t>Gana Bélgica</t>
   </si>
   <si>
@@ -233,9 +230,6 @@
     <t>Gana Croacia</t>
   </si>
   <si>
-    <t>Gana Corea</t>
-  </si>
-  <si>
     <t>Gana Estados Unidos</t>
   </si>
   <si>
@@ -257,13 +251,22 @@
     <t>Gana Francia</t>
   </si>
   <si>
-    <t>Gana Irán</t>
-  </si>
-  <si>
     <t>Gana Austria</t>
   </si>
   <si>
     <t>Gana Portugal</t>
+  </si>
+  <si>
+    <t>Gana Turquía</t>
+  </si>
+  <si>
+    <t>Gana Holanda</t>
+  </si>
+  <si>
+    <t>Gana México</t>
+  </si>
+  <si>
+    <t>Gana Egipto</t>
   </si>
 </sst>
 </file>
@@ -442,6 +445,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -461,27 +485,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -835,26 +838,26 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -876,22 +879,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -913,22 +916,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -950,22 +953,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -988,22 +991,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1025,22 +1028,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1062,22 +1065,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1099,22 +1102,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1136,22 +1139,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1174,22 +1177,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1211,22 +1214,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1248,22 +1251,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1285,22 +1288,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1322,22 +1325,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1360,22 +1363,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1397,22 +1400,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1434,22 +1437,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1471,22 +1474,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1508,22 +1511,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1546,22 +1549,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1583,22 +1586,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1620,22 +1623,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1657,22 +1660,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1694,22 +1697,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1731,22 +1734,22 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1768,11 +1771,11 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1780,42 +1783,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1832,6 +1799,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B053078-BA77-4CA5-A64A-6DBF88E011FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7AA768-EC00-416D-AC2A-BDDF4901189D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -227,9 +227,6 @@
     <t>Gana Argentina</t>
   </si>
   <si>
-    <t>Gana Croacia</t>
-  </si>
-  <si>
     <t>Gana Estados Unidos</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>Gana Noruega</t>
   </si>
   <si>
-    <t>Gana Ecuador</t>
-  </si>
-  <si>
     <t>Gana Japón</t>
   </si>
   <si>
@@ -267,6 +261,12 @@
   </si>
   <si>
     <t>Gana Egipto</t>
+  </si>
+  <si>
+    <t>Gana Inglaterra</t>
+  </si>
+  <si>
+    <t>Gana Alemania</t>
   </si>
 </sst>
 </file>
@@ -445,27 +445,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -485,6 +464,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -838,26 +838,26 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -879,22 +879,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -916,22 +916,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -953,22 +953,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -991,22 +991,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1028,22 +1028,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1065,22 +1065,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1102,22 +1102,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1139,22 +1139,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1177,22 +1177,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1214,22 +1214,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1251,22 +1251,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1288,22 +1288,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1325,22 +1325,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1363,22 +1363,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1400,22 +1400,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1437,22 +1437,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1474,22 +1474,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1511,22 +1511,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1549,22 +1549,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1586,22 +1586,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1623,22 +1623,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1660,22 +1660,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1697,22 +1697,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1734,22 +1734,22 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1771,11 +1771,11 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1783,6 +1783,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1799,42 +1835,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7AA768-EC00-416D-AC2A-BDDF4901189D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2030D1E1-7A96-4AA4-A4B7-6CEF14FC8EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="77">
   <si>
     <t>Partido 1</t>
   </si>
@@ -445,6 +445,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -464,27 +485,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -838,26 +838,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -879,22 +877,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -916,22 +914,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -953,22 +951,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -991,22 +989,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1028,22 +1026,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1065,22 +1063,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1102,22 +1100,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1139,22 +1137,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1177,22 +1175,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1214,22 +1212,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1251,22 +1249,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1288,22 +1286,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1325,22 +1323,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1363,22 +1361,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1400,22 +1398,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1437,22 +1435,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1474,22 +1472,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1511,22 +1509,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1549,22 +1547,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1586,22 +1584,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1623,22 +1621,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1660,22 +1658,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1697,22 +1695,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1734,22 +1732,22 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1771,11 +1769,11 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1783,42 +1781,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1835,6 +1797,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2030D1E1-7A96-4AA4-A4B7-6CEF14FC8EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA7B18E-0053-4EFC-8840-0AFD769D6FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,60 +213,6 @@
   </si>
   <si>
     <t>Colombia</t>
-  </si>
-  <si>
-    <t>Gana Paraguay</t>
-  </si>
-  <si>
-    <t>Gana Brasil</t>
-  </si>
-  <si>
-    <t>Gana Bélgica</t>
-  </si>
-  <si>
-    <t>Gana Argentina</t>
-  </si>
-  <si>
-    <t>Gana Estados Unidos</t>
-  </si>
-  <si>
-    <t>Gana Suiza</t>
-  </si>
-  <si>
-    <t>Gana Noruega</t>
-  </si>
-  <si>
-    <t>Gana Japón</t>
-  </si>
-  <si>
-    <t>Gana España</t>
-  </si>
-  <si>
-    <t>Gana Francia</t>
-  </si>
-  <si>
-    <t>Gana Austria</t>
-  </si>
-  <si>
-    <t>Gana Portugal</t>
-  </si>
-  <si>
-    <t>Gana Turquía</t>
-  </si>
-  <si>
-    <t>Gana Holanda</t>
-  </si>
-  <si>
-    <t>Gana México</t>
-  </si>
-  <si>
-    <t>Gana Egipto</t>
-  </si>
-  <si>
-    <t>Gana Inglaterra</t>
-  </si>
-  <si>
-    <t>Gana Alemania</t>
   </si>
 </sst>
 </file>
@@ -445,27 +391,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -485,6 +410,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -838,24 +784,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -877,22 +823,20 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -914,22 +858,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -951,22 +893,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -989,22 +929,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1026,22 +964,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1063,22 +999,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1100,22 +1034,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1137,22 +1069,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1175,22 +1105,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1212,22 +1140,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1249,22 +1175,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1286,22 +1210,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1323,22 +1245,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1361,22 +1281,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1398,22 +1316,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1435,22 +1351,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1472,22 +1386,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1509,22 +1421,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1547,22 +1457,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1584,22 +1492,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1621,22 +1527,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1658,22 +1562,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1695,22 +1597,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1732,22 +1632,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1769,11 +1667,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1781,6 +1677,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1797,42 +1729,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA7B18E-0053-4EFC-8840-0AFD769D6FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE0A8CE-D4AA-47B4-A514-E556FCA9DA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="60">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>Colombia</t>
+  </si>
+  <si>
+    <t>Gana México</t>
   </si>
 </sst>
 </file>
@@ -391,6 +394,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -410,27 +434,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,24 +787,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -823,20 +826,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -858,20 +863,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -893,20 +898,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -929,20 +934,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -964,20 +969,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -999,20 +1004,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1034,20 +1039,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1069,20 +1074,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1105,20 +1110,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1140,20 +1145,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1175,20 +1180,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1210,20 +1215,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1245,20 +1250,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1281,20 +1286,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1316,20 +1321,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1351,20 +1356,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1386,20 +1391,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1421,20 +1426,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1457,20 +1462,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1492,20 +1497,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1527,20 +1532,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1562,20 +1567,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1597,20 +1602,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1632,20 +1637,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1667,9 +1672,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1677,42 +1682,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1729,6 +1698,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE0A8CE-D4AA-47B4-A514-E556FCA9DA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B923BECB-F344-4BDD-B049-57DA97E9D5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
   <si>
     <t>Partido 1</t>
   </si>
@@ -394,27 +394,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -434,6 +413,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -787,24 +787,26 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -826,22 +828,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -863,20 +865,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -898,20 +900,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -934,20 +936,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -969,20 +971,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1004,20 +1006,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1039,20 +1041,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1074,20 +1076,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1110,20 +1112,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1145,20 +1147,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1180,20 +1182,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1215,20 +1217,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1250,20 +1252,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1286,20 +1288,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1321,20 +1323,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1356,20 +1358,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1391,20 +1393,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1426,20 +1428,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1462,20 +1464,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1497,20 +1499,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1532,20 +1534,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1567,20 +1569,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1602,20 +1604,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1637,20 +1639,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1672,9 +1674,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1682,6 +1684,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1698,42 +1736,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B923BECB-F344-4BDD-B049-57DA97E9D5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07254A7F-22B7-4178-B5AD-E0D0EE783A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,9 +213,6 @@
   </si>
   <si>
     <t>Colombia</t>
-  </si>
-  <si>
-    <t>Gana México</t>
   </si>
 </sst>
 </file>
@@ -394,6 +391,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -413,27 +431,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -787,26 +784,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -828,22 +823,20 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -865,20 +858,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -900,20 +893,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -936,20 +929,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -971,20 +964,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1006,20 +999,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1041,20 +1034,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1076,20 +1069,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1112,20 +1105,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1147,20 +1140,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1182,20 +1175,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1217,20 +1210,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1252,20 +1245,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1288,20 +1281,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1323,20 +1316,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1358,20 +1351,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1393,20 +1386,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1428,20 +1421,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1464,20 +1457,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1499,20 +1492,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1534,20 +1527,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1569,20 +1562,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1604,20 +1597,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1639,20 +1632,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1674,9 +1667,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1684,42 +1677,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1736,6 +1693,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07254A7F-22B7-4178-B5AD-E0D0EE783A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDEAB6E-CDA7-4EB4-B89A-53166DB63FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -391,27 +391,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -431,6 +410,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,24 +784,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -823,20 +823,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -858,20 +860,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -893,20 +895,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -929,20 +931,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -964,20 +966,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -999,20 +1001,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1034,20 +1036,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1069,20 +1071,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1105,20 +1107,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1140,20 +1142,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1175,20 +1177,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1210,20 +1212,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1245,20 +1247,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1281,20 +1283,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1316,20 +1318,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1351,20 +1353,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1386,20 +1388,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1421,20 +1423,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1457,20 +1459,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1492,20 +1494,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1527,20 +1529,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1562,20 +1564,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1597,20 +1599,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1632,20 +1634,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1667,9 +1669,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1677,6 +1679,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1693,42 +1731,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDEAB6E-CDA7-4EB4-B89A-53166DB63FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11FF4F7-5F65-4D7D-9C88-CD85DF0FE48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -391,6 +391,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -410,27 +431,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,24 +784,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -823,22 +823,20 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -860,20 +858,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -895,20 +893,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -931,20 +929,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -966,20 +964,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1001,20 +999,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1036,20 +1034,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1071,20 +1069,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1107,20 +1105,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1142,20 +1140,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1177,20 +1175,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1212,20 +1210,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1247,20 +1245,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1283,20 +1281,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1318,20 +1316,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1353,20 +1351,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1388,20 +1386,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1423,20 +1421,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1459,20 +1457,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1494,20 +1492,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1529,20 +1527,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1564,20 +1562,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1599,20 +1597,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1634,20 +1632,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1669,9 +1667,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1679,42 +1677,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1731,6 +1693,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11FF4F7-5F65-4D7D-9C88-CD85DF0FE48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13F0D92-D813-44C8-B15A-AD37C371BF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-4485" yWindow="-10440" windowWidth="14400" windowHeight="7275" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="60">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>Colombia</t>
+  </si>
+  <si>
+    <t>Gana México</t>
   </si>
 </sst>
 </file>
@@ -391,27 +394,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -431,6 +413,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,24 +787,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -823,20 +826,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -858,20 +863,20 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -893,20 +898,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -929,20 +934,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -964,20 +969,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -999,20 +1004,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1034,20 +1039,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1069,20 +1074,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1105,20 +1110,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1140,20 +1145,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1175,20 +1180,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1210,20 +1215,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1245,20 +1250,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1281,20 +1286,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1316,20 +1321,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1351,20 +1356,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1386,20 +1391,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1421,20 +1426,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1457,20 +1462,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1492,20 +1497,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1527,20 +1532,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1562,20 +1567,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1597,20 +1602,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1632,20 +1637,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1667,9 +1672,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1677,6 +1682,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1693,42 +1734,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13F0D92-D813-44C8-B15A-AD37C371BF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66338A7E-1818-418A-9B1E-CBEBFC092892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4485" yWindow="-10440" windowWidth="14400" windowHeight="7275" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="61">
   <si>
     <t>Partido 1</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>Gana México</t>
+  </si>
+  <si>
+    <t>Gana Estados Unidos</t>
   </si>
 </sst>
 </file>
@@ -394,6 +397,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -413,27 +437,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -787,24 +790,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -826,22 +829,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -863,20 +866,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -898,20 +903,20 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -934,20 +939,20 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -969,20 +974,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1004,20 +1009,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1039,20 +1044,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1074,20 +1079,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1110,20 +1115,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1145,20 +1150,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1180,20 +1185,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1215,20 +1220,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1250,20 +1255,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1286,20 +1291,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1321,20 +1326,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1356,20 +1361,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1391,20 +1396,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1426,20 +1431,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1462,20 +1467,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1497,20 +1502,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1532,20 +1537,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1567,20 +1572,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1602,20 +1607,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1637,20 +1642,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1672,9 +1677,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1682,42 +1687,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1734,6 +1703,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66338A7E-1818-418A-9B1E-CBEBFC092892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EB9399-885A-4EB1-A725-F9B14311E9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
   <si>
     <t>Partido 1</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>Gana Estados Unidos</t>
+  </si>
+  <si>
+    <t>Gana Australia</t>
   </si>
 </sst>
 </file>
@@ -397,27 +400,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -437,6 +419,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -790,24 +793,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -829,22 +832,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -866,22 +869,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -903,20 +906,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -939,20 +944,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -974,20 +981,20 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1009,20 +1016,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1044,20 +1051,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1079,20 +1086,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1115,20 +1122,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1150,20 +1157,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1185,20 +1192,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1220,20 +1227,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1255,20 +1262,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1291,20 +1298,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1326,20 +1333,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1361,20 +1368,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1396,20 +1403,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1431,20 +1438,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1467,20 +1474,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1502,20 +1509,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1537,20 +1544,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1572,20 +1579,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1607,20 +1614,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1642,20 +1649,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1677,9 +1684,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1687,6 +1694,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1703,42 +1746,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EB9399-885A-4EB1-A725-F9B14311E9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38D0D2F-0F37-4809-895A-7F8F4679FE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="63">
   <si>
     <t>Partido 1</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Gana Australia</t>
+  </si>
+  <si>
+    <t>Gana Holanda</t>
   </si>
 </sst>
 </file>
@@ -400,6 +403,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -419,27 +443,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -793,24 +796,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -832,22 +835,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -869,22 +872,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -906,22 +909,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -944,22 +947,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -981,20 +984,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1016,20 +1021,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1051,20 +1056,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1086,20 +1091,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1122,20 +1127,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1157,20 +1162,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1192,20 +1197,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1227,20 +1232,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1262,20 +1267,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1298,20 +1303,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1333,20 +1338,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1368,20 +1373,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1403,20 +1408,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1438,20 +1443,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1474,20 +1479,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1509,20 +1514,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1544,20 +1549,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1579,20 +1584,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1614,20 +1619,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1649,20 +1654,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1684,9 +1689,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1694,42 +1699,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1746,6 +1715,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38D0D2F-0F37-4809-895A-7F8F4679FE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AB2331-08BA-4A0D-8CE6-1F2030EA6BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="62">
   <si>
     <t>Partido 1</t>
   </si>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>Gana Australia</t>
-  </si>
-  <si>
-    <t>Gana Holanda</t>
   </si>
 </sst>
 </file>
@@ -403,27 +400,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -443,6 +419,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -796,24 +793,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -835,22 +832,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -872,22 +869,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -909,22 +906,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -947,22 +944,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -984,22 +981,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1021,20 +1018,20 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1056,20 +1053,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1091,20 +1088,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1127,20 +1124,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1162,20 +1159,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1197,20 +1194,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1232,20 +1229,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1267,20 +1264,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1303,20 +1300,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1338,20 +1335,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1373,20 +1370,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1408,20 +1405,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1443,20 +1440,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1479,20 +1476,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1514,20 +1511,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1549,20 +1546,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1584,20 +1581,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1619,20 +1616,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1654,20 +1651,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1689,9 +1686,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1699,6 +1696,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1715,42 +1748,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AB2331-08BA-4A0D-8CE6-1F2030EA6BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07523112-A77D-4732-B53F-226EF2DEB6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>Partido 1</t>
   </si>
@@ -400,6 +400,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -419,27 +440,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -793,24 +793,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -832,22 +832,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -869,22 +869,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -906,22 +906,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -944,22 +944,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -981,22 +981,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1018,20 +1018,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1053,20 +1055,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1088,20 +1090,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1124,20 +1126,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1159,20 +1161,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1194,20 +1196,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1229,20 +1231,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1264,20 +1266,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1300,20 +1302,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1335,20 +1337,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1370,20 +1372,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1405,20 +1407,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1440,20 +1442,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1476,20 +1478,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1511,20 +1513,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1546,20 +1548,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1581,20 +1583,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1616,20 +1618,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1651,20 +1653,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1686,9 +1688,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1696,42 +1698,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1748,6 +1714,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07523112-A77D-4732-B53F-226EF2DEB6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882599E7-CE4F-4223-AA20-530991221B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>Partido 1</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Gana Australia</t>
+  </si>
+  <si>
+    <t>Gana Egipto</t>
   </si>
 </sst>
 </file>
@@ -400,27 +403,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -440,6 +422,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -793,24 +796,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -832,22 +835,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -869,22 +872,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -906,22 +909,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -944,22 +947,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -981,22 +984,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1018,22 +1021,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1055,20 +1058,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1090,20 +1093,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1126,20 +1129,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1161,20 +1164,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1196,20 +1199,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1231,20 +1234,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1266,20 +1269,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1302,20 +1305,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1337,20 +1340,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1372,20 +1375,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1407,20 +1410,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1442,20 +1445,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1478,20 +1481,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1513,20 +1516,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1548,20 +1551,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1583,20 +1586,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1618,20 +1621,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1653,20 +1656,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1688,9 +1691,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1698,6 +1701,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1714,42 +1753,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882599E7-CE4F-4223-AA20-530991221B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92BF55A-ABE0-4C67-B664-092BB3DC4D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>Partido 1</t>
   </si>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>Gana Australia</t>
-  </si>
-  <si>
-    <t>Gana Egipto</t>
   </si>
 </sst>
 </file>
@@ -403,6 +400,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -422,27 +440,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -796,24 +793,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -835,22 +832,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -872,22 +869,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -909,22 +906,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -947,22 +944,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -984,22 +981,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1021,22 +1018,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1058,20 +1055,20 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1093,20 +1090,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1129,20 +1126,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1164,20 +1161,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1199,20 +1196,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1234,20 +1231,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1269,20 +1266,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1305,20 +1302,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1340,20 +1337,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1375,20 +1372,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1410,20 +1407,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1445,20 +1442,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1481,20 +1478,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1516,20 +1513,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1551,20 +1548,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1586,20 +1583,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1621,20 +1618,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1656,20 +1653,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1691,9 +1688,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1701,42 +1698,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1753,6 +1714,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92BF55A-ABE0-4C67-B664-092BB3DC4D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49CAAFE-83E8-40EB-96C6-FF048EDAC83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="63">
   <si>
     <t>Partido 1</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Gana Australia</t>
+  </si>
+  <si>
+    <t>Gana Francia</t>
   </si>
 </sst>
 </file>
@@ -400,27 +403,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -440,6 +422,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -793,24 +796,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -832,22 +835,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -869,22 +872,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -906,22 +909,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -944,22 +947,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -981,22 +984,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1018,22 +1021,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1055,20 +1058,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1090,20 +1095,20 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1126,20 +1131,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1161,20 +1166,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1196,20 +1201,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1231,20 +1236,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1266,20 +1271,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1302,20 +1307,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1337,20 +1342,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1372,20 +1377,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1407,20 +1412,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1442,20 +1447,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1478,20 +1483,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1513,20 +1518,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1548,20 +1553,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1583,20 +1588,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1618,20 +1623,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1653,20 +1658,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1688,9 +1693,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1698,6 +1703,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1714,42 +1755,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49CAAFE-83E8-40EB-96C6-FF048EDAC83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C212EC-8671-46FC-AE57-709875D0DF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="64">
   <si>
     <t>Partido 1</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>Gana Francia</t>
+  </si>
+  <si>
+    <t>Gana Argentina</t>
   </si>
 </sst>
 </file>
@@ -403,6 +406,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -422,27 +446,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -796,24 +799,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -835,22 +838,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -872,22 +875,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -909,22 +912,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -947,22 +950,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -984,22 +987,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1021,22 +1024,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1058,22 +1061,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1095,20 +1098,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="B36" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1131,20 +1136,20 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1166,20 +1171,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1201,20 +1206,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1236,20 +1241,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1271,20 +1276,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1307,20 +1312,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1342,20 +1347,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1377,20 +1382,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1412,20 +1417,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1447,20 +1452,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1483,20 +1488,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1518,20 +1523,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1553,20 +1558,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1588,20 +1593,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1623,20 +1628,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1658,20 +1663,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1693,9 +1698,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1703,42 +1708,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1755,6 +1724,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C212EC-8671-46FC-AE57-709875D0DF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13570902-656D-4687-9366-CC68FA439482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
   <si>
     <t>Partido 1</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>Gana Argentina</t>
+  </si>
+  <si>
+    <t>Gana Inglaterra</t>
   </si>
 </sst>
 </file>
@@ -406,27 +409,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -446,6 +428,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -799,24 +802,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -838,22 +841,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -875,22 +878,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -912,22 +915,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -950,22 +953,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -987,22 +990,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1024,22 +1027,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1061,22 +1064,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1098,22 +1101,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1136,20 +1139,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1171,20 +1176,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1206,20 +1211,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1241,20 +1246,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1276,20 +1281,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1312,20 +1317,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1347,20 +1352,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1382,20 +1387,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1417,20 +1422,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1452,20 +1457,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1488,20 +1493,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1523,20 +1528,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1558,20 +1563,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1593,20 +1598,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1628,20 +1633,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1663,20 +1668,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1698,9 +1703,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1708,6 +1713,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1724,42 +1765,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13570902-656D-4687-9366-CC68FA439482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB7B1F3-09BB-48B9-82F3-D528D90F020C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
   <si>
     <t>Partido 1</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>Gana Argentina</t>
-  </si>
-  <si>
-    <t>Gana Inglaterra</t>
   </si>
 </sst>
 </file>
@@ -409,6 +406,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -428,27 +446,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -802,24 +799,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -841,22 +838,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -878,22 +875,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -915,22 +912,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -953,22 +950,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -990,22 +987,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1027,22 +1024,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1064,22 +1061,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1101,22 +1098,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1139,22 +1136,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1176,20 +1173,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1211,20 +1208,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1246,20 +1243,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1281,20 +1278,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1317,20 +1314,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1352,20 +1349,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1387,20 +1384,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1422,20 +1419,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1457,20 +1454,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1493,20 +1490,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1528,20 +1525,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1563,20 +1560,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1598,20 +1595,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1633,20 +1630,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1668,20 +1665,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1703,9 +1700,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1713,42 +1710,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1765,6 +1726,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB7B1F3-09BB-48B9-82F3-D528D90F020C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB14C3E-B9EF-42BE-BD8A-728AC30483AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
   <si>
     <t>Partido 1</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>Gana Argentina</t>
+  </si>
+  <si>
+    <t>Gana Inglaterra</t>
   </si>
 </sst>
 </file>
@@ -406,27 +409,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -446,6 +428,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -799,24 +802,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -838,22 +841,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -875,22 +878,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -912,22 +915,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -950,22 +953,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -987,22 +990,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1024,22 +1027,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1061,22 +1064,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1098,22 +1101,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1136,22 +1139,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1173,20 +1176,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1208,20 +1211,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1243,20 +1246,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1278,20 +1281,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1314,20 +1317,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1349,20 +1352,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1384,20 +1387,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1419,20 +1422,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1454,20 +1457,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1490,20 +1493,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1525,20 +1528,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1560,20 +1563,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1595,20 +1598,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1630,20 +1633,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1665,20 +1668,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1700,9 +1703,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1710,6 +1713,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1726,42 +1765,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB14C3E-B9EF-42BE-BD8A-728AC30483AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEAC8B4-AD83-43ED-AD01-D5C2E00F611E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
   <si>
     <t>Partido 1</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>Gana Argentina</t>
-  </si>
-  <si>
-    <t>Gana Inglaterra</t>
   </si>
 </sst>
 </file>
@@ -409,6 +406,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -428,27 +446,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -802,24 +799,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -841,22 +838,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -878,22 +875,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -915,22 +912,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -953,22 +950,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -990,22 +987,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1027,22 +1024,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1064,22 +1061,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1101,22 +1098,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1139,22 +1136,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="B40" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1176,20 +1173,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1211,20 +1208,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1246,20 +1243,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1281,20 +1278,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1317,20 +1314,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1352,20 +1349,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1387,20 +1384,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1422,20 +1419,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1457,20 +1454,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1493,20 +1490,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1528,20 +1525,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1563,20 +1560,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1598,20 +1595,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1633,20 +1630,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1668,20 +1665,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1703,9 +1700,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1713,42 +1710,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1765,6 +1726,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEAC8B4-AD83-43ED-AD01-D5C2E00F611E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99F5FE1-4293-46D0-A0C1-C5E82B686FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-7650" yWindow="-15030" windowWidth="21600" windowHeight="11175" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
   <si>
     <t>Partido 1</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>Gana Argentina</t>
+  </si>
+  <si>
+    <t>Gana Inglaterra</t>
   </si>
 </sst>
 </file>
@@ -406,27 +409,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -446,6 +428,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -799,24 +802,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -838,22 +841,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -875,22 +878,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -912,22 +915,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -950,22 +953,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -987,22 +990,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1024,22 +1027,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1061,22 +1064,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1098,22 +1101,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1136,22 +1139,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1173,20 +1176,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1208,20 +1211,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1243,20 +1246,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1278,20 +1281,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1314,20 +1317,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1349,20 +1352,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1384,20 +1387,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1419,20 +1422,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1454,20 +1457,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1490,20 +1493,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1525,20 +1528,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1560,20 +1563,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1595,20 +1598,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1630,20 +1633,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1665,20 +1668,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1700,9 +1703,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1710,6 +1713,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1726,42 +1765,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99F5FE1-4293-46D0-A0C1-C5E82B686FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996D56CD-9AAD-4410-96DA-2422DDAF84AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7650" yWindow="-15030" windowWidth="21600" windowHeight="11175" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -409,6 +409,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -428,27 +449,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -802,24 +802,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -841,22 +841,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -878,22 +878,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -915,22 +915,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -953,22 +953,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -990,22 +990,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1027,22 +1027,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1064,22 +1064,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1101,22 +1101,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1139,22 +1139,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1176,20 +1176,20 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1211,20 +1211,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1246,20 +1246,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1281,20 +1281,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1317,20 +1317,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1352,20 +1352,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1387,20 +1387,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1422,20 +1422,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1457,20 +1457,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1493,20 +1493,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1528,20 +1528,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1563,20 +1563,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1598,20 +1598,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1633,20 +1633,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1668,20 +1668,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1703,9 +1703,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1713,42 +1713,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1765,6 +1729,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996D56CD-9AAD-4410-96DA-2422DDAF84AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF344A0-7F22-4C90-915D-06C402399228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="65">
   <si>
     <t>Partido 1</t>
   </si>
@@ -409,27 +409,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -449,6 +428,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -802,24 +802,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -841,22 +841,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -878,22 +878,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -915,22 +915,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -953,22 +953,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -990,22 +990,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1027,22 +1027,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1064,22 +1064,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1101,22 +1101,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1139,22 +1139,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1176,20 +1176,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1211,20 +1213,20 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1246,20 +1248,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1281,20 +1283,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1317,20 +1319,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1352,20 +1354,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1387,20 +1389,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1422,20 +1424,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1457,20 +1459,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1493,20 +1495,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1528,20 +1530,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1563,20 +1565,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1598,20 +1600,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1633,20 +1635,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1668,20 +1670,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1703,9 +1705,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1713,6 +1715,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1729,42 +1767,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF344A0-7F22-4C90-915D-06C402399228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EA9E8D-241B-4F0F-AD05-AA242A615115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="65">
   <si>
     <t>Partido 1</t>
   </si>
@@ -409,6 +409,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -428,27 +449,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -802,24 +802,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -841,22 +841,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -878,22 +878,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -915,22 +915,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -953,22 +953,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -990,22 +990,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1027,22 +1027,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1064,22 +1064,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1101,22 +1101,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1139,22 +1139,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1176,22 +1176,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1213,20 +1213,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="B48" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1248,20 +1250,20 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1283,20 +1285,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1319,20 +1321,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1354,20 +1356,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1389,20 +1391,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1424,20 +1426,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1459,20 +1461,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1495,20 +1497,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1530,20 +1532,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1565,20 +1567,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1600,20 +1602,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1635,20 +1637,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1670,20 +1672,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1705,9 +1707,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1715,42 +1717,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1767,6 +1733,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EA9E8D-241B-4F0F-AD05-AA242A615115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C19592F-DB7A-46CB-850B-C60A089E0FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="66">
   <si>
     <t>Partido 1</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>Gana Inglaterra</t>
+  </si>
+  <si>
+    <t>Gana Holanda</t>
   </si>
 </sst>
 </file>
@@ -409,27 +412,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -449,6 +431,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -802,24 +805,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -841,22 +844,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -878,22 +881,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -915,22 +918,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -953,22 +956,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -990,22 +993,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1027,22 +1030,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1064,22 +1067,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1101,22 +1104,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1139,22 +1142,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1176,22 +1179,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1213,22 +1216,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1250,20 +1253,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="B52" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1285,20 +1290,20 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1321,20 +1326,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1356,20 +1361,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1391,20 +1396,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1426,20 +1431,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1461,20 +1466,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1497,20 +1502,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1532,20 +1537,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1567,20 +1572,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1602,20 +1607,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1637,20 +1642,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1672,20 +1677,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1707,9 +1712,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1717,6 +1722,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1733,42 +1774,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C19592F-DB7A-46CB-850B-C60A089E0FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25DE39E-117C-4203-B003-72349783A33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="66">
   <si>
     <t>Partido 1</t>
   </si>
@@ -412,6 +412,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -431,27 +452,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -805,24 +805,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -844,22 +844,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -881,22 +881,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -918,22 +918,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -956,22 +956,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -993,22 +993,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1030,22 +1030,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1067,22 +1067,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1104,22 +1104,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1142,22 +1142,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1179,22 +1179,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1216,22 +1216,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1253,22 +1253,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1290,20 +1290,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1326,20 +1328,20 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1361,20 +1363,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1396,20 +1398,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1431,20 +1433,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1466,20 +1468,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1502,20 +1504,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1537,20 +1539,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1572,20 +1574,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1607,20 +1609,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1642,20 +1644,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1677,20 +1679,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1712,9 +1714,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1722,42 +1724,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1774,6 +1740,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25DE39E-117C-4203-B003-72349783A33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2115B8D8-15B3-4714-B7B7-1B9452E32CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
   <si>
     <t>Partido 1</t>
   </si>
@@ -412,27 +412,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -452,6 +431,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -805,24 +805,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -844,22 +844,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -881,22 +881,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -918,22 +918,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -956,22 +956,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -993,22 +993,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1030,22 +1030,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1067,22 +1067,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1104,22 +1104,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1142,22 +1142,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1179,22 +1179,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1216,22 +1216,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1253,22 +1253,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1290,22 +1290,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1328,20 +1328,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="B60" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1363,20 +1365,20 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1398,20 +1400,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1433,20 +1435,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1468,20 +1470,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1504,20 +1506,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1539,20 +1541,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1574,20 +1576,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1609,20 +1611,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1644,20 +1646,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1679,20 +1681,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1714,9 +1716,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1724,6 +1726,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1740,42 +1778,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2115B8D8-15B3-4714-B7B7-1B9452E32CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF6FC7A-775A-47F2-B303-AE4CEB6557ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
   <si>
     <t>Partido 1</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>Gana Holanda</t>
+  </si>
+  <si>
+    <t>Gana Noruega</t>
   </si>
 </sst>
 </file>
@@ -412,6 +415,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -431,27 +455,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -805,24 +808,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -844,22 +847,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -881,22 +884,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -918,22 +921,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -956,22 +959,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -993,22 +996,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1030,22 +1033,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1067,22 +1070,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1104,22 +1107,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1142,22 +1145,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1179,22 +1182,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1216,22 +1219,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1253,22 +1256,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1290,22 +1293,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1328,22 +1331,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1365,20 +1368,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="B64" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1400,20 +1405,20 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1435,20 +1440,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1470,20 +1475,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1506,20 +1511,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1541,20 +1546,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1576,20 +1581,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1611,20 +1616,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1646,20 +1651,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1681,20 +1686,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1716,9 +1721,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1726,42 +1731,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1778,6 +1747,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF6FC7A-775A-47F2-B303-AE4CEB6557ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BAEA6A-0D99-4302-9BE2-3AA216706A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
   <si>
     <t>Partido 1</t>
   </si>
@@ -237,13 +237,16 @@
   </si>
   <si>
     <t>Gana Noruega</t>
+  </si>
+  <si>
+    <t>Gana Suiza</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,27 +418,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -455,6 +437,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -797,41 +800,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F1176-9B5F-4509-AEB9-C4D2AF7AA58E}">
   <dimension ref="B2:H104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.54296875" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" customWidth="1"/>
-    <col min="3" max="3" width="3.54296875" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
-    <col min="8" max="8" width="21.81640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+    <row r="2" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="3" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-    </row>
-    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
-    </row>
-    <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="6" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:8" ht="14.5" thickBot="1">
       <c r="B7" s="4" t="s">
         <v>37</v>
       </c>
@@ -846,29 +849,29 @@
         <v>Gana Sudáfrica</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+    <row r="8" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+    <row r="9" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="10" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="14.5" thickBot="1">
       <c r="B11" s="4" t="s">
         <v>40</v>
       </c>
@@ -883,29 +886,29 @@
         <v>Gana Paraguay</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+    <row r="13" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="14" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:8" ht="14.5" thickBot="1">
       <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
@@ -920,29 +923,29 @@
         <v>Gana Marruecos</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+    <row r="16" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+    <row r="17" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="18" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" ht="14.5" thickBot="1">
       <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
@@ -958,29 +961,29 @@
         <v>Gana Turquía</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+    <row r="20" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+    <row r="21" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="22" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" ht="14.5" thickBot="1">
       <c r="B23" s="4" t="s">
         <v>45</v>
       </c>
@@ -995,29 +998,29 @@
         <v>Gana Japón</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+    <row r="24" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+    <row r="25" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="26" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" ht="14.5" thickBot="1">
       <c r="B27" s="4" t="s">
         <v>46</v>
       </c>
@@ -1032,29 +1035,29 @@
         <v>Gana Egipto</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+    <row r="28" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+    <row r="29" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="30" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:8" ht="14.5" thickBot="1">
       <c r="B31" s="4" t="s">
         <v>5</v>
       </c>
@@ -1069,29 +1072,29 @@
         <v>Gana Senegal</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+    <row r="32" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+    <row r="33" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="34" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:8" ht="14.5" thickBot="1">
       <c r="B35" s="4" t="s">
         <v>10</v>
       </c>
@@ -1106,29 +1109,29 @@
         <v>Gana Argelia</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+    <row r="36" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+    <row r="37" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="38" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:8" ht="14.5" thickBot="1">
       <c r="B39" s="4" t="s">
         <v>49</v>
       </c>
@@ -1144,29 +1147,29 @@
         <v>Gana Croacia</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+    <row r="40" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+    <row r="41" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="42" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:8" ht="14.5" thickBot="1">
       <c r="B43" s="4" t="s">
         <v>37</v>
       </c>
@@ -1181,29 +1184,29 @@
         <v>Gana Corea</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+    <row r="44" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+    <row r="45" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="46" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:8" ht="14.5" thickBot="1">
       <c r="B47" s="4" t="s">
         <v>40</v>
       </c>
@@ -1218,29 +1221,29 @@
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+    <row r="48" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+    <row r="49" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="50" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
       </c>
     </row>
-    <row r="51" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:8" ht="14.5" thickBot="1">
       <c r="B51" s="4" t="s">
         <v>45</v>
       </c>
@@ -1255,29 +1258,29 @@
         <v>Gana Suecia</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
+    <row r="52" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+    <row r="53" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="54" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
       </c>
     </row>
-    <row r="55" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:8" ht="14.5" thickBot="1">
       <c r="B55" s="4" t="s">
         <v>46</v>
       </c>
@@ -1292,29 +1295,29 @@
         <v>Gana Irán</v>
       </c>
     </row>
-    <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+    <row r="56" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+    <row r="57" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="58" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
       </c>
     </row>
-    <row r="59" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:8" ht="14.5" thickBot="1">
       <c r="B59" s="4" t="s">
         <v>10</v>
       </c>
@@ -1330,29 +1333,29 @@
         <v>Gana Austria</v>
       </c>
     </row>
-    <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+    <row r="60" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B60" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+    <row r="61" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="62" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:8" ht="14.5" thickBot="1">
       <c r="B63" s="4" t="s">
         <v>53</v>
       </c>
@@ -1367,29 +1370,29 @@
         <v>Gana Senegal</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
+    <row r="64" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B64" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+    <row r="65" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="66" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:8" ht="14.5" thickBot="1">
       <c r="B67" s="4" t="s">
         <v>54</v>
       </c>
@@ -1404,27 +1407,29 @@
         <v>Gana Canadá</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+    <row r="68" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B68" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+    <row r="69" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="70" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:8" ht="14.5" thickBot="1">
       <c r="B71" s="4" t="s">
         <v>56</v>
       </c>
@@ -1439,27 +1444,27 @@
         <v>Gana Alemania</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+    <row r="72" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+    <row r="73" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="74" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:8" ht="14.5" thickBot="1">
       <c r="B75" s="4" t="s">
         <v>27</v>
       </c>
@@ -1474,27 +1479,27 @@
         <v>Gana Suecia</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+    <row r="76" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+    <row r="77" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="78" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:8" ht="14.5" thickBot="1">
       <c r="B79" s="4" t="s">
         <v>44</v>
       </c>
@@ -1510,27 +1515,27 @@
         <v>Gana Estados Unidos</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+    <row r="80" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+    <row r="81" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="82" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="14.5" thickBot="1">
       <c r="B83" s="4" t="s">
         <v>41</v>
       </c>
@@ -1545,27 +1550,27 @@
         <v>Gana Australia</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+    <row r="84" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+    <row r="85" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="86" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="14.5" thickBot="1">
       <c r="B87" s="4" t="s">
         <v>57</v>
       </c>
@@ -1580,27 +1585,27 @@
         <v>Gana España</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+    <row r="88" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+    <row r="89" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="90" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:8" ht="14.5" thickBot="1">
       <c r="B91" s="4" t="s">
         <v>53</v>
       </c>
@@ -1615,27 +1620,27 @@
         <v>Gana Francia</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+    <row r="92" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+    <row r="93" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="94" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:8" ht="14.5" thickBot="1">
       <c r="B95" s="4" t="s">
         <v>47</v>
       </c>
@@ -1650,27 +1655,27 @@
         <v>Gana Irán</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+    <row r="96" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+    <row r="97" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="98" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:8" ht="14.5" thickBot="1">
       <c r="B99" s="4" t="s">
         <v>48</v>
       </c>
@@ -1685,27 +1690,27 @@
         <v>Gana Austria</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+    <row r="100" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+    <row r="101" spans="2:8" ht="14.5" thickBot="1"/>
+    <row r="102" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:8" ht="14.5" thickBot="1">
       <c r="B103" s="4" t="s">
         <v>58</v>
       </c>
@@ -1720,10 +1725,10 @@
         <v>Gana Portugal</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+    <row r="104" spans="2:8" ht="14.5" thickBot="1">
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1731,6 +1736,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1747,42 +1788,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BAEA6A-0D99-4302-9BE2-3AA216706A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B43405C-821C-4430-BDD3-03F8679D8AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
   <si>
     <t>Partido 1</t>
   </si>
@@ -237,9 +237,6 @@
   </si>
   <si>
     <t>Gana Noruega</t>
-  </si>
-  <si>
-    <t>Gana Suiza</t>
   </si>
 </sst>
 </file>
@@ -1408,9 +1405,7 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B68" s="12" t="s">
-        <v>67</v>
-      </c>
+      <c r="B68" s="12"/>
       <c r="C68" s="13"/>
       <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF6FC7A-775A-47F2-B303-AE4CEB6557ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A91780F-FDD2-40F2-8BDC-DB3E873C36BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
   <si>
     <t>Partido 1</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>Gana Noruega</t>
+  </si>
+  <si>
+    <t>Gana Suiza</t>
   </si>
 </sst>
 </file>
@@ -415,27 +418,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -455,6 +437,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -808,24 +811,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -847,22 +850,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -884,22 +887,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -921,22 +924,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -959,22 +962,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -996,22 +999,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1033,22 +1036,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1070,22 +1073,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1107,22 +1110,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1145,22 +1148,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1182,22 +1185,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1219,22 +1222,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1256,22 +1259,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1293,22 +1296,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1331,22 +1334,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1368,22 +1371,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1405,20 +1408,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="B68" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1440,20 +1445,20 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1475,20 +1480,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1511,20 +1516,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1546,20 +1551,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1581,20 +1586,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1616,20 +1621,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1651,20 +1656,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1686,20 +1691,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1721,9 +1726,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1731,6 +1736,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1747,42 +1788,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A91780F-FDD2-40F2-8BDC-DB3E873C36BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E292E0E0-C529-47C5-9C3C-89205008F6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="68">
   <si>
     <t>Partido 1</t>
   </si>
@@ -418,6 +418,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -437,27 +458,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -811,24 +811,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -850,22 +850,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -887,22 +887,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -924,22 +924,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -962,22 +962,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -999,22 +999,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1036,22 +1036,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1073,22 +1073,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1110,22 +1110,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1148,22 +1148,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1185,22 +1185,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1222,22 +1222,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1259,22 +1259,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1296,22 +1296,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1334,22 +1334,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1371,22 +1371,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1408,22 +1408,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1445,20 +1445,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1480,20 +1482,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1516,20 +1518,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1551,20 +1553,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1586,20 +1588,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1621,20 +1623,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1656,20 +1658,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1691,20 +1693,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1726,9 +1728,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1736,42 +1738,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1788,6 +1754,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E292E0E0-C529-47C5-9C3C-89205008F6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E408B07-EB5C-4944-86FA-C538FAD3CC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="69">
   <si>
     <t>Partido 1</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>Gana Suiza</t>
+  </si>
+  <si>
+    <t>Gana Ecuador</t>
   </si>
 </sst>
 </file>
@@ -418,27 +421,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -458,6 +440,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -811,24 +814,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -850,22 +853,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -887,22 +890,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -924,22 +927,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -962,22 +965,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -999,22 +1002,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1036,22 +1039,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1073,22 +1076,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1110,22 +1113,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1148,22 +1151,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1185,22 +1188,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1222,22 +1225,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1259,22 +1262,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1296,22 +1299,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1334,22 +1337,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1371,22 +1374,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1408,22 +1411,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1445,22 +1448,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="B72" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1482,20 +1485,20 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1518,20 +1521,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1553,20 +1556,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1588,20 +1591,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1623,20 +1626,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1658,20 +1661,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1693,20 +1696,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1728,9 +1731,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1738,6 +1741,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1754,42 +1793,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E408B07-EB5C-4944-86FA-C538FAD3CC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0E43A6-EB93-487C-B871-35F1C6DB01EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="69">
   <si>
     <t>Partido 1</t>
   </si>
@@ -421,6 +421,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -440,27 +461,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -814,24 +814,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -853,22 +853,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -890,22 +890,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -927,22 +927,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -965,22 +965,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1002,22 +1002,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1039,22 +1039,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1076,22 +1076,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1113,22 +1113,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1151,22 +1151,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1188,22 +1188,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1225,22 +1225,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1262,22 +1262,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1299,22 +1299,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1337,22 +1337,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1374,22 +1374,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1411,22 +1411,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1448,22 +1448,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1485,20 +1485,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1521,20 +1523,20 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1556,20 +1558,20 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1591,20 +1593,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1626,20 +1628,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1661,20 +1663,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1696,20 +1698,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1731,9 +1733,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1741,42 +1743,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1793,6 +1759,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0E43A6-EB93-487C-B871-35F1C6DB01EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F954F02A-3A7B-4E00-BAD1-DA051B771CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="70">
   <si>
     <t>Partido 1</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>Gana Ecuador</t>
+  </si>
+  <si>
+    <t>Gana Turquía</t>
   </si>
 </sst>
 </file>
@@ -421,27 +424,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -461,6 +443,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -814,24 +817,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -853,22 +856,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -890,22 +893,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -927,22 +930,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -965,22 +968,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1002,22 +1005,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1039,22 +1042,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1076,22 +1079,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1113,22 +1116,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1151,22 +1154,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1188,22 +1191,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1225,22 +1228,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1262,22 +1265,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1299,22 +1302,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1337,22 +1340,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1374,22 +1377,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1411,22 +1414,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1448,22 +1451,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1485,22 +1488,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1523,20 +1526,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="B80" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1558,20 +1563,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1593,20 +1600,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1628,20 +1635,20 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1663,20 +1670,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1698,20 +1705,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1733,9 +1740,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1743,6 +1750,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1759,42 +1802,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F954F02A-3A7B-4E00-BAD1-DA051B771CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E78464-9422-4F0A-861D-DAD4A4705BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="70">
   <si>
     <t>Partido 1</t>
   </si>
@@ -424,6 +424,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -443,27 +464,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -817,24 +817,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -856,22 +856,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -893,22 +893,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -930,22 +930,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -968,22 +968,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1005,22 +1005,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1042,22 +1042,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1079,22 +1079,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1116,22 +1116,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1154,22 +1154,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1191,22 +1191,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1228,22 +1228,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1265,22 +1265,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1302,22 +1302,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1340,22 +1340,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1377,22 +1377,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1414,22 +1414,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1451,22 +1451,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1488,22 +1488,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1526,22 +1526,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1563,22 +1563,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1600,20 +1600,20 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1635,20 +1635,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="B92" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1670,20 +1672,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1705,20 +1707,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1740,9 +1742,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1750,42 +1752,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1802,6 +1768,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E78464-9422-4F0A-861D-DAD4A4705BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE68DAB-F05B-4D13-9446-4B40309F2294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="71">
   <si>
     <t>Partido 1</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>Gana Turquía</t>
+  </si>
+  <si>
+    <t>Gana España</t>
   </si>
 </sst>
 </file>
@@ -424,27 +427,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -464,6 +446,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -817,24 +820,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -856,22 +859,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -893,22 +896,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -930,22 +933,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -968,22 +971,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1005,22 +1008,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1042,22 +1045,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1079,22 +1082,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1116,22 +1119,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1154,22 +1157,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1191,22 +1194,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1228,22 +1231,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1265,22 +1268,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1302,22 +1305,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1340,22 +1343,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1377,22 +1380,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1414,22 +1417,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1451,22 +1454,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1488,22 +1491,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1526,22 +1529,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1563,22 +1566,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1600,20 +1603,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="B88" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1635,22 +1640,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1672,20 +1677,20 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1707,20 +1712,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1742,9 +1747,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1752,6 +1757,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1768,42 +1809,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE68DAB-F05B-4D13-9446-4B40309F2294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59F946C-CBF9-491F-98EF-1F447865D434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="71">
   <si>
     <t>Partido 1</t>
   </si>
@@ -427,6 +427,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -446,27 +467,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -820,24 +820,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -859,22 +859,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -896,22 +896,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -933,22 +933,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -971,22 +971,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1008,22 +1008,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1045,22 +1045,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1082,22 +1082,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1119,22 +1119,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1157,22 +1157,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1194,22 +1194,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1231,22 +1231,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1268,22 +1268,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1305,22 +1305,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1343,22 +1343,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1380,22 +1380,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1417,22 +1417,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1454,22 +1454,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1491,22 +1491,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1529,22 +1529,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1566,22 +1566,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1603,22 +1603,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1640,22 +1640,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1677,20 +1677,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1712,20 +1714,20 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1747,9 +1749,9 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1757,42 +1759,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1809,6 +1775,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59F946C-CBF9-491F-98EF-1F447865D434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAAD3F8-0613-46C3-ACB4-5F0F2F74AA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="71">
   <si>
     <t>Partido 1</t>
   </si>
@@ -427,27 +427,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -467,6 +446,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -820,24 +820,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -859,22 +859,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -896,22 +896,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -933,22 +933,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -971,22 +971,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1008,22 +1008,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1045,22 +1045,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1082,22 +1082,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1119,22 +1119,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1157,22 +1157,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1194,22 +1194,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1231,22 +1231,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1268,22 +1268,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1305,22 +1305,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1343,22 +1343,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1380,22 +1380,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1417,22 +1417,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1454,22 +1454,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1491,22 +1491,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1529,22 +1529,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1566,22 +1566,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1603,22 +1603,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1640,22 +1640,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1677,22 +1677,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1714,20 +1714,22 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1749,9 +1751,11 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1759,6 +1763,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1775,42 +1815,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAAD3F8-0613-46C3-ACB4-5F0F2F74AA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8327AD-7547-4DB1-8B01-28B5C28FE4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -427,6 +427,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -446,27 +467,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -820,24 +820,24 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -859,22 +859,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -896,22 +896,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -933,22 +933,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -971,22 +971,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1008,22 +1008,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1045,22 +1045,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1082,22 +1082,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1119,22 +1119,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1157,22 +1157,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1194,22 +1194,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1231,22 +1231,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1268,22 +1268,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1305,22 +1305,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
+      <c r="B56" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1343,22 +1343,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1380,22 +1380,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1417,22 +1417,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1454,22 +1454,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1491,22 +1491,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
+      <c r="B76" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1529,22 +1529,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1566,22 +1566,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
+      <c r="B84" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1603,22 +1603,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1640,22 +1640,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1677,22 +1677,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
+      <c r="B96" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1714,22 +1714,22 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
+      <c r="B100" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1751,11 +1751,11 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
+      <c r="B104" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="10"/>
+      <c r="D104" s="11"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1763,42 +1763,6 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1815,6 +1779,42 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8327AD-7547-4DB1-8B01-28B5C28FE4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3936D3A6-D1FB-4004-BEA0-1ADD99FD1A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Pauta/E01Pauta.xlsx
+++ b/Pauta/E01Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3936D3A6-D1FB-4004-BEA0-1ADD99FD1A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC7F833-0021-413E-8604-BC2E2E72C5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
   <si>
     <t>Partido 1</t>
   </si>
@@ -427,27 +427,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -467,6 +446,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -820,24 +820,26 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="H6" s="2" t="str">
         <f>"Gana "&amp;B7</f>
         <v>Gana México</v>
@@ -859,22 +861,22 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2" t="str">
         <f>"Gana "&amp;B11</f>
         <v>Gana Estados Unidos</v>
@@ -896,22 +898,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
       <c r="H12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="H14" s="2" t="str">
         <f>"Gana "&amp;B15</f>
         <v>Gana Brasil</v>
@@ -933,22 +935,22 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="H18" s="2" t="str">
         <f>"Gana "&amp;B19</f>
         <v>Gana Australia</v>
@@ -971,22 +973,22 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
       <c r="H22" s="2" t="str">
         <f>"Gana "&amp;B23</f>
         <v>Gana Holanda</v>
@@ -1008,22 +1010,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
       <c r="H24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="H26" s="2" t="str">
         <f>"Gana "&amp;B27</f>
         <v>Gana Bélgica</v>
@@ -1045,22 +1047,22 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
       <c r="H28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="H30" s="2" t="str">
         <f>"Gana "&amp;B31</f>
         <v>Gana Francia</v>
@@ -1082,22 +1084,22 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="H32" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="H34" s="2" t="str">
         <f>"Gana "&amp;B35</f>
         <v>Gana Argentina</v>
@@ -1119,22 +1121,22 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
       <c r="H36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="H38" s="2" t="str">
         <f>"Gana "&amp;B39</f>
         <v>Gana Inglaterra</v>
@@ -1157,22 +1159,22 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
       <c r="H40" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
       <c r="H42" s="2" t="str">
         <f>"Gana "&amp;B43</f>
         <v>Gana México</v>
@@ -1194,22 +1196,22 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
       <c r="H44" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
       <c r="H46" s="2" t="str">
         <f>"Gana "&amp;B47</f>
         <v>Gana Estados Unidos</v>
@@ -1231,22 +1233,22 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
       <c r="H48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="50" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
       <c r="H50" s="2" t="str">
         <f>"Gana "&amp;B51</f>
         <v>Gana Holanda</v>
@@ -1268,22 +1270,22 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
       <c r="H52" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="54" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="H54" s="2" t="str">
         <f>"Gana "&amp;B55</f>
         <v>Gana Bélgica</v>
@@ -1305,22 +1307,22 @@
       </c>
     </row>
     <row r="56" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
       <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
       <c r="H58" s="2" t="str">
         <f>"Gana "&amp;B59</f>
         <v>Gana Argentina</v>
@@ -1343,22 +1345,22 @@
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="11"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
       <c r="H60" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="62" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
       <c r="H62" s="2" t="str">
         <f>"Gana "&amp;B63</f>
         <v>Gana Noruega</v>
@@ -1380,22 +1382,22 @@
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
       <c r="H64" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="8"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
       <c r="H66" s="2" t="str">
         <f>"Gana "&amp;B67</f>
         <v>Gana Suiza</v>
@@ -1417,22 +1419,22 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
       <c r="H68" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="70" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="8"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
       <c r="H70" s="2" t="str">
         <f>"Gana "&amp;B71</f>
         <v>Gana Ecuador</v>
@@ -1454,22 +1456,22 @@
       </c>
     </row>
     <row r="72" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="H72" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="8"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
       <c r="H74" s="2" t="str">
         <f>"Gana "&amp;B75</f>
         <v>Gana Japón</v>
@@ -1491,22 +1493,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="B76" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
       <c r="H76" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="78" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="8"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
       <c r="H78" s="2" t="str">
         <f>"Gana "&amp;B79</f>
         <v>Gana Turquía</v>
@@ -1529,22 +1531,22 @@
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
       <c r="H80" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="8"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
       <c r="H82" s="2" t="str">
         <f>"Gana "&amp;B83</f>
         <v>Gana Paraguay</v>
@@ -1566,22 +1568,22 @@
       </c>
     </row>
     <row r="84" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="B84" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
       <c r="H84" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="8"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
       <c r="H86" s="2" t="str">
         <f>"Gana "&amp;B87</f>
         <v>Gana Uruguay</v>
@@ -1603,22 +1605,22 @@
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
       <c r="H88" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="90" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="8"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
       <c r="H90" s="2" t="str">
         <f>"Gana "&amp;B91</f>
         <v>Gana Noruega</v>
@@ -1640,22 +1642,22 @@
       </c>
     </row>
     <row r="92" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
       <c r="H92" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="8"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
       <c r="H94" s="2" t="str">
         <f>"Gana "&amp;B95</f>
         <v>Gana Egipto</v>
@@ -1677,22 +1679,22 @@
       </c>
     </row>
     <row r="96" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="B96" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
       <c r="H96" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="98" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="8"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
       <c r="H98" s="2" t="str">
         <f>"Gana "&amp;B99</f>
         <v>Gana Argelia</v>
@@ -1714,22 +1716,22 @@
       </c>
     </row>
     <row r="100" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="B100" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
       <c r="H100" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="102" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="8"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
       <c r="H102" s="2" t="str">
         <f>"Gana "&amp;B103</f>
         <v>Gana Colombia</v>
@@ -1751,11 +1753,11 @@
       </c>
     </row>
     <row r="104" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="11"/>
+      <c r="B104" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
       <c r="H104" s="2" t="s">
         <v>1</v>
       </c>
@@ -1763,6 +1765,42 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="52">
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B96:D96"/>
@@ -1779,42 +1817,6 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B76:D76"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B100 B96 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64 B68 B72 B76 B80 B84 B88 B92 B104" xr:uid="{5B958DC4-58BD-46F0-BD6B-4A983C6D99F0}">
